--- a/results/0916-all/蒙宁甘农牧区/tech_selected_summary.xlsx
+++ b/results/0916-all/蒙宁甘农牧区/tech_selected_summary.xlsx
@@ -166,217 +166,217 @@
     <t>中宁县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 6142.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>6142.92</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>EEF(CRF)_maize</t>
@@ -385,7 +385,7 @@
     <t>4R(Right place)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 27055513.50</t>
+    <t>27055513.50</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -520,16 +520,16 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 508719236.73</t>
+    <t>508719236.73</t>
   </si>
   <si>
     <t>rolller press_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 62055.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 3874319.94</t>
+    <t>62055.00</t>
+  </si>
+  <si>
+    <t>3874319.94</t>
   </si>
   <si>
     <t>Biochar_beef cattle</t>
@@ -547,7 +547,7 @@
     <t>EEF(NI)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 288605506.02</t>
+    <t>288605506.02</t>
   </si>
   <si>
     <t>Nitrocompounds_dairy</t>
@@ -568,7 +568,7 @@
     <t>4R(Right rate)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 63611542.88</t>
+    <t>63611542.88</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
@@ -580,7 +580,7 @@
     <t>Physical additives_pig</t>
   </si>
   <si>
-    <t>总经济成本: 99316366.05</t>
+    <t>99316366.05</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -589,13 +589,13 @@
     <t>compost（low）≤30%_maize</t>
   </si>
   <si>
-    <t>总经济成本: 87590287.01</t>
-  </si>
-  <si>
-    <t>总经济成本: 12902016.81</t>
-  </si>
-  <si>
-    <t>总经济成本: 18157544.91</t>
+    <t>87590287.01</t>
+  </si>
+  <si>
+    <t>12902016.81</t>
+  </si>
+  <si>
+    <t>18157544.91</t>
   </si>
   <si>
     <t>Yucca extract_Beef cattle</t>
@@ -637,10 +637,10 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 575876534.82</t>
-  </si>
-  <si>
-    <t>总经济成本: 562207470.50</t>
+    <t>575876534.82</t>
+  </si>
+  <si>
+    <t>562207470.50</t>
   </si>
   <si>
     <t>Frequent removal_beef cattle</t>
@@ -649,40 +649,40 @@
     <t>EEF(NI)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 463717182.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 2811079.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 99014462.46</t>
-  </si>
-  <si>
-    <t>总经济成本: 135950634.29</t>
-  </si>
-  <si>
-    <t>总经济成本: 528913656.18</t>
-  </si>
-  <si>
-    <t>总经济成本: 396543890.33</t>
-  </si>
-  <si>
-    <t>总经济成本: 262469355.88</t>
+    <t>463717182.86</t>
+  </si>
+  <si>
+    <t>2811079.58</t>
+  </si>
+  <si>
+    <t>99014462.46</t>
+  </si>
+  <si>
+    <t>135950634.29</t>
+  </si>
+  <si>
+    <t>528913656.18</t>
+  </si>
+  <si>
+    <t>396543890.33</t>
+  </si>
+  <si>
+    <t>262469355.88</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 257970431.13</t>
-  </si>
-  <si>
-    <t>总经济成本: 13510574.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 75869301.96</t>
-  </si>
-  <si>
-    <t>总经济成本: 145205245.46</t>
+    <t>257970431.13</t>
+  </si>
+  <si>
+    <t>13510574.00</t>
+  </si>
+  <si>
+    <t>75869301.96</t>
+  </si>
+  <si>
+    <t>145205245.46</t>
   </si>
 </sst>
 </file>
